--- a/5/search/FY5_Missile1_results/solutions_direction_90.0.xlsx
+++ b/5/search/FY5_Missile1_results/solutions_direction_90.0.xlsx
@@ -490,7 +490,7 @@
         <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>100.8</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -502,7 +502,7 @@
         <v>13000</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
@@ -511,7 +511,7 @@
         <v>13000</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1300</v>
